--- a/InputData/fuels/PEIIR/Pollutant Emissions Intensity Improvement Rate.xlsx
+++ b/InputData/fuels/PEIIR/Pollutant Emissions Intensity Improvement Rate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\fuels\PEIIR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\fuels\PEIIR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E3BD0C-A423-4B33-9496-E16F34203A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB088B64-F7AE-4F98-B0F4-14E551481D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="783" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="60840" yWindow="2385" windowWidth="24900" windowHeight="14490" tabRatio="783" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="76">
   <si>
     <t>Source:</t>
   </si>
@@ -279,6 +279,12 @@
   </si>
   <si>
     <t>hydrogen combined cycle</t>
+  </si>
+  <si>
+    <t>green hydrogen</t>
+  </si>
+  <si>
+    <t>low carbon hydrogen</t>
   </si>
 </sst>
 </file>
@@ -683,33 +689,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="1" max="1" width="16.7265625" customWidth="1"/>
     <col min="2" max="2" width="73" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
@@ -717,97 +723,97 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>53</v>
       </c>
@@ -823,21 +829,21 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" customWidth="1"/>
-    <col min="9" max="9" width="15.28515625" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" customWidth="1"/>
-    <col min="11" max="11" width="11.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.7265625" customWidth="1"/>
+    <col min="5" max="5" width="14.1796875" customWidth="1"/>
+    <col min="6" max="6" width="18.26953125" customWidth="1"/>
+    <col min="8" max="8" width="13.26953125" customWidth="1"/>
+    <col min="9" max="9" width="15.26953125" customWidth="1"/>
+    <col min="10" max="10" width="13.54296875" customWidth="1"/>
+    <col min="11" max="13" width="11.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>64</v>
       </c>
@@ -871,8 +877,14 @@
       <c r="K1" s="4" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -906,8 +918,14 @@
       <c r="K2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -941,8 +959,14 @@
       <c r="K3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -976,8 +1000,14 @@
       <c r="K4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1011,8 +1041,14 @@
       <c r="K5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1046,8 +1082,14 @@
       <c r="K6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1081,8 +1123,14 @@
       <c r="K7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1116,8 +1164,14 @@
       <c r="K8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1151,8 +1205,14 @@
       <c r="K9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1186,8 +1246,14 @@
       <c r="K10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1221,8 +1287,14 @@
       <c r="K11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1256,8 +1328,14 @@
       <c r="K12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1289,6 +1367,12 @@
         <v>0</v>
       </c>
       <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
         <v>0</v>
       </c>
     </row>
@@ -1304,21 +1388,21 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" customWidth="1"/>
+    <col min="5" max="5" width="18.54296875" customWidth="1"/>
+    <col min="6" max="6" width="18.26953125" customWidth="1"/>
+    <col min="7" max="7" width="16.54296875" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" customWidth="1"/>
+    <col min="10" max="10" width="13.1796875" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>64</v>
       </c>
@@ -1353,7 +1437,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1388,7 +1472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1423,7 +1507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1458,7 +1542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1493,7 +1577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1528,7 +1612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1563,7 +1647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1598,7 +1682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1633,7 +1717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1668,7 +1752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1703,7 +1787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1738,7 +1822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1785,21 +1869,21 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" customWidth="1"/>
+    <col min="3" max="3" width="14.26953125" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" customWidth="1"/>
+    <col min="5" max="5" width="18.54296875" customWidth="1"/>
+    <col min="6" max="6" width="18.26953125" customWidth="1"/>
+    <col min="7" max="7" width="16.54296875" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" customWidth="1"/>
+    <col min="10" max="10" width="13.1796875" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>64</v>
       </c>
@@ -1834,7 +1918,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1869,7 +1953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1904,7 +1988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1939,7 +2023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1974,7 +2058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2009,7 +2093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2044,7 +2128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -2079,7 +2163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -2114,7 +2198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -2149,7 +2233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -2184,7 +2268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -2219,7 +2303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2266,21 +2350,21 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" customWidth="1"/>
+    <col min="3" max="3" width="12.81640625" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" customWidth="1"/>
+    <col min="5" max="5" width="18.54296875" customWidth="1"/>
+    <col min="6" max="6" width="18.26953125" customWidth="1"/>
+    <col min="7" max="7" width="16.54296875" customWidth="1"/>
+    <col min="8" max="8" width="14.54296875" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" customWidth="1"/>
+    <col min="10" max="10" width="13.1796875" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>64</v>
       </c>
@@ -2315,7 +2399,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -2350,7 +2434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2385,7 +2469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2420,7 +2504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -2455,7 +2539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2490,7 +2574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2525,7 +2609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -2560,7 +2644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -2595,7 +2679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -2630,7 +2714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -2665,7 +2749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -2700,7 +2784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2747,21 +2831,21 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" customWidth="1"/>
+    <col min="3" max="3" width="13.54296875" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" customWidth="1"/>
+    <col min="5" max="5" width="18.54296875" customWidth="1"/>
+    <col min="6" max="6" width="18.26953125" customWidth="1"/>
+    <col min="7" max="7" width="16.54296875" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" customWidth="1"/>
+    <col min="10" max="10" width="13.1796875" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>64</v>
       </c>
@@ -2796,7 +2880,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -2831,7 +2915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2866,7 +2950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2901,7 +2985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -2936,7 +3020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2971,7 +3055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3006,7 +3090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -3041,7 +3125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -3076,7 +3160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -3111,7 +3195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -3146,7 +3230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -3181,7 +3265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -3228,21 +3312,21 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" customWidth="1"/>
+    <col min="5" max="5" width="18.54296875" customWidth="1"/>
+    <col min="6" max="6" width="18.26953125" customWidth="1"/>
+    <col min="7" max="7" width="16.54296875" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" customWidth="1"/>
+    <col min="10" max="10" width="13.1796875" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>64</v>
       </c>
@@ -3277,7 +3361,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -3312,7 +3396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3347,7 +3431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3382,7 +3466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3417,7 +3501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -3452,7 +3536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3487,7 +3571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -3522,7 +3606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -3557,7 +3641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -3592,7 +3676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -3627,7 +3711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -3662,7 +3746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -3709,21 +3793,21 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" customWidth="1"/>
+    <col min="5" max="5" width="18.54296875" customWidth="1"/>
+    <col min="6" max="6" width="18.26953125" customWidth="1"/>
+    <col min="7" max="7" width="16.54296875" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" customWidth="1"/>
+    <col min="10" max="10" width="13.1796875" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>64</v>
       </c>
@@ -3758,7 +3842,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -3793,7 +3877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3828,7 +3912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3863,7 +3947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3898,7 +3982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -3933,7 +4017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3968,7 +4052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -4003,7 +4087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -4038,7 +4122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -4073,7 +4157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -4108,7 +4192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -4143,7 +4227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -4190,27 +4274,27 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:Y13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.81640625" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="23" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" customWidth="1"/>
+    <col min="6" max="6" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.26953125" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" customWidth="1"/>
-    <col min="13" max="13" width="20.7109375" customWidth="1"/>
-    <col min="14" max="14" width="13.7109375" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.140625" customWidth="1"/>
-    <col min="17" max="17" width="17.140625" customWidth="1"/>
-    <col min="18" max="18" width="15.5703125" customWidth="1"/>
-    <col min="19" max="24" width="13.42578125" customWidth="1"/>
+    <col min="10" max="10" width="12.7265625" customWidth="1"/>
+    <col min="11" max="11" width="15.7265625" customWidth="1"/>
+    <col min="12" max="12" width="16.1796875" customWidth="1"/>
+    <col min="13" max="13" width="20.7265625" customWidth="1"/>
+    <col min="14" max="14" width="13.7265625" customWidth="1"/>
+    <col min="15" max="15" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.1796875" customWidth="1"/>
+    <col min="17" max="17" width="17.1796875" customWidth="1"/>
+    <col min="18" max="18" width="15.54296875" customWidth="1"/>
+    <col min="19" max="24" width="13.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>64</v>
       </c>
@@ -4287,7 +4371,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -4364,7 +4448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -4441,7 +4525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4518,7 +4602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -4595,7 +4679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -4672,7 +4756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -4749,7 +4833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -4826,7 +4910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -4903,7 +4987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -4980,7 +5064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -5057,7 +5141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -5134,7 +5218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -5223,20 +5307,20 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.140625" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" customWidth="1"/>
+    <col min="3" max="3" width="16.7265625" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
-    <col min="10" max="10" width="22.85546875" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" customWidth="1"/>
+    <col min="8" max="8" width="13.26953125" customWidth="1"/>
+    <col min="9" max="9" width="24.7265625" customWidth="1"/>
+    <col min="10" max="10" width="22.81640625" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>64</v>
       </c>
@@ -5271,7 +5355,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -5306,7 +5390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -5341,7 +5425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -5376,7 +5460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -5411,7 +5495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -5446,7 +5530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -5481,7 +5565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -5516,7 +5600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -5551,7 +5635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -5586,7 +5670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -5621,7 +5705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -5656,7 +5740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>

--- a/InputData/fuels/PEIIR/Pollutant Emissions Intensity Improvement Rate.xlsx
+++ b/InputData/fuels/PEIIR/Pollutant Emissions Intensity Improvement Rate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\fuels\PEIIR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\fuels\PEIIR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB088B64-F7AE-4F98-B0F4-14E551481D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E3BD0C-A423-4B33-9496-E16F34203A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60840" yWindow="2385" windowWidth="24900" windowHeight="14490" tabRatio="783" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="783" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="74">
   <si>
     <t>Source:</t>
   </si>
@@ -279,12 +279,6 @@
   </si>
   <si>
     <t>hydrogen combined cycle</t>
-  </si>
-  <si>
-    <t>green hydrogen</t>
-  </si>
-  <si>
-    <t>low carbon hydrogen</t>
   </si>
 </sst>
 </file>
@@ -689,33 +683,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B34"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.7265625" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
     <col min="2" max="2" width="73" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
@@ -723,97 +717,97 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>53</v>
       </c>
@@ -829,21 +823,21 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13.7265625" customWidth="1"/>
-    <col min="5" max="5" width="14.1796875" customWidth="1"/>
-    <col min="6" max="6" width="18.26953125" customWidth="1"/>
-    <col min="8" max="8" width="13.26953125" customWidth="1"/>
-    <col min="9" max="9" width="15.26953125" customWidth="1"/>
-    <col min="10" max="10" width="13.54296875" customWidth="1"/>
-    <col min="11" max="13" width="11.54296875" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" customWidth="1"/>
+    <col min="11" max="11" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>64</v>
       </c>
@@ -877,14 +871,8 @@
       <c r="K1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="L1" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -918,14 +906,8 @@
       <c r="K2">
         <v>0</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -959,14 +941,8 @@
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1000,14 +976,8 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1041,14 +1011,8 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1082,14 +1046,8 @@
       <c r="K6">
         <v>0</v>
       </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1123,14 +1081,8 @@
       <c r="K7">
         <v>0</v>
       </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1164,14 +1116,8 @@
       <c r="K8">
         <v>0</v>
       </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1205,14 +1151,8 @@
       <c r="K9">
         <v>0</v>
       </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1246,14 +1186,8 @@
       <c r="K10">
         <v>0</v>
       </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1287,14 +1221,8 @@
       <c r="K11">
         <v>0</v>
       </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1328,14 +1256,8 @@
       <c r="K12">
         <v>0</v>
       </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1367,12 +1289,6 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
         <v>0</v>
       </c>
     </row>
@@ -1388,21 +1304,21 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.26953125" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="21.453125" customWidth="1"/>
-    <col min="5" max="5" width="18.54296875" customWidth="1"/>
-    <col min="6" max="6" width="18.26953125" customWidth="1"/>
-    <col min="7" max="7" width="16.54296875" customWidth="1"/>
-    <col min="8" max="8" width="11.1796875" customWidth="1"/>
-    <col min="9" max="9" width="15.54296875" customWidth="1"/>
-    <col min="10" max="10" width="13.1796875" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>64</v>
       </c>
@@ -1437,7 +1353,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1472,7 +1388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1507,7 +1423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1542,7 +1458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1577,7 +1493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1612,7 +1528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1647,7 +1563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1682,7 +1598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1717,7 +1633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1752,7 +1668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1787,7 +1703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1822,7 +1738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1869,21 +1785,21 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.26953125" customWidth="1"/>
-    <col min="3" max="3" width="14.26953125" customWidth="1"/>
-    <col min="4" max="4" width="21.453125" customWidth="1"/>
-    <col min="5" max="5" width="18.54296875" customWidth="1"/>
-    <col min="6" max="6" width="18.26953125" customWidth="1"/>
-    <col min="7" max="7" width="16.54296875" customWidth="1"/>
-    <col min="8" max="8" width="11.1796875" customWidth="1"/>
-    <col min="9" max="9" width="15.54296875" customWidth="1"/>
-    <col min="10" max="10" width="13.1796875" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>64</v>
       </c>
@@ -1918,7 +1834,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1953,7 +1869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1988,7 +1904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2023,7 +1939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -2058,7 +1974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2093,7 +2009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2128,7 +2044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -2163,7 +2079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -2198,7 +2114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -2233,7 +2149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -2268,7 +2184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -2303,7 +2219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2350,21 +2266,21 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.26953125" customWidth="1"/>
-    <col min="3" max="3" width="12.81640625" customWidth="1"/>
-    <col min="4" max="4" width="21.453125" customWidth="1"/>
-    <col min="5" max="5" width="18.54296875" customWidth="1"/>
-    <col min="6" max="6" width="18.26953125" customWidth="1"/>
-    <col min="7" max="7" width="16.54296875" customWidth="1"/>
-    <col min="8" max="8" width="14.54296875" customWidth="1"/>
-    <col min="9" max="9" width="15.54296875" customWidth="1"/>
-    <col min="10" max="10" width="13.1796875" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>64</v>
       </c>
@@ -2399,7 +2315,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -2434,7 +2350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2469,7 +2385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2504,7 +2420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -2539,7 +2455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2574,7 +2490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2609,7 +2525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -2644,7 +2560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -2679,7 +2595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -2714,7 +2630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -2749,7 +2665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -2784,7 +2700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2831,21 +2747,21 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.26953125" customWidth="1"/>
-    <col min="3" max="3" width="13.54296875" customWidth="1"/>
-    <col min="4" max="4" width="21.453125" customWidth="1"/>
-    <col min="5" max="5" width="18.54296875" customWidth="1"/>
-    <col min="6" max="6" width="18.26953125" customWidth="1"/>
-    <col min="7" max="7" width="16.54296875" customWidth="1"/>
-    <col min="8" max="8" width="11.1796875" customWidth="1"/>
-    <col min="9" max="9" width="15.54296875" customWidth="1"/>
-    <col min="10" max="10" width="13.1796875" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>64</v>
       </c>
@@ -2880,7 +2796,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -2915,7 +2831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2950,7 +2866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2985,7 +2901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3020,7 +2936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -3055,7 +2971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3090,7 +3006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -3125,7 +3041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -3160,7 +3076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -3195,7 +3111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -3230,7 +3146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -3265,7 +3181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -3312,21 +3228,21 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.26953125" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="21.453125" customWidth="1"/>
-    <col min="5" max="5" width="18.54296875" customWidth="1"/>
-    <col min="6" max="6" width="18.26953125" customWidth="1"/>
-    <col min="7" max="7" width="16.54296875" customWidth="1"/>
-    <col min="8" max="8" width="11.1796875" customWidth="1"/>
-    <col min="9" max="9" width="15.54296875" customWidth="1"/>
-    <col min="10" max="10" width="13.1796875" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>64</v>
       </c>
@@ -3361,7 +3277,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -3396,7 +3312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3431,7 +3347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3466,7 +3382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3501,7 +3417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -3536,7 +3452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3571,7 +3487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -3606,7 +3522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -3641,7 +3557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -3676,7 +3592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -3711,7 +3627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -3746,7 +3662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -3793,21 +3709,21 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.26953125" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" customWidth="1"/>
-    <col min="4" max="4" width="21.453125" customWidth="1"/>
-    <col min="5" max="5" width="18.54296875" customWidth="1"/>
-    <col min="6" max="6" width="18.26953125" customWidth="1"/>
-    <col min="7" max="7" width="16.54296875" customWidth="1"/>
-    <col min="8" max="8" width="11.1796875" customWidth="1"/>
-    <col min="9" max="9" width="15.54296875" customWidth="1"/>
-    <col min="10" max="10" width="13.1796875" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>64</v>
       </c>
@@ -3842,7 +3758,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -3877,7 +3793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3912,7 +3828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3947,7 +3863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3982,7 +3898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -4017,7 +3933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -4052,7 +3968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -4087,7 +4003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -4122,7 +4038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -4157,7 +4073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -4192,7 +4108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -4227,7 +4143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -4274,27 +4190,27 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:Y13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.81640625" customWidth="1"/>
-    <col min="2" max="2" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="23" customWidth="1"/>
-    <col min="6" max="6" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.26953125" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="12.7265625" customWidth="1"/>
-    <col min="11" max="11" width="15.7265625" customWidth="1"/>
-    <col min="12" max="12" width="16.1796875" customWidth="1"/>
-    <col min="13" max="13" width="20.7265625" customWidth="1"/>
-    <col min="14" max="14" width="13.7265625" customWidth="1"/>
-    <col min="15" max="15" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.1796875" customWidth="1"/>
-    <col min="17" max="17" width="17.1796875" customWidth="1"/>
-    <col min="18" max="18" width="15.54296875" customWidth="1"/>
-    <col min="19" max="24" width="13.453125" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" customWidth="1"/>
+    <col min="12" max="12" width="16.140625" customWidth="1"/>
+    <col min="13" max="13" width="20.7109375" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" customWidth="1"/>
+    <col min="15" max="15" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.140625" customWidth="1"/>
+    <col min="17" max="17" width="17.140625" customWidth="1"/>
+    <col min="18" max="18" width="15.5703125" customWidth="1"/>
+    <col min="19" max="24" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:25" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>64</v>
       </c>
@@ -4371,7 +4287,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -4448,7 +4364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -4525,7 +4441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4602,7 +4518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -4679,7 +4595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -4756,7 +4672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -4833,7 +4749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -4910,7 +4826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -4987,7 +4903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -5064,7 +4980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -5141,7 +5057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -5218,7 +5134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -5307,20 +5223,20 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.1796875" customWidth="1"/>
-    <col min="3" max="3" width="16.7265625" customWidth="1"/>
-    <col min="4" max="4" width="16.81640625" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="7" max="7" width="14.7265625" customWidth="1"/>
-    <col min="8" max="8" width="13.26953125" customWidth="1"/>
-    <col min="9" max="9" width="24.7265625" customWidth="1"/>
-    <col min="10" max="10" width="22.81640625" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="10" max="10" width="22.85546875" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>64</v>
       </c>
@@ -5355,7 +5271,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -5390,7 +5306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -5425,7 +5341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -5460,7 +5376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -5495,7 +5411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -5530,7 +5446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -5565,7 +5481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -5600,7 +5516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -5635,7 +5551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -5670,7 +5586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -5705,7 +5621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -5740,7 +5656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
